--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,116 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-19 15:32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4aadfd8469de6c639bcf548dc9c928da_1784475078.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-19 15:34</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2c195a65d0d8235ab541cbd8802027fa_1784475250.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1123,116 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f5d4056bdcef037358a5b450a14ec943_1784563741.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6fb124a8cf385f21760216378f778e6f_1784563931.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,116 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/5d3f82f2f683c7443ccb60820d1bd05e.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ceeb949e5487ce76621ac6e1821ab20_1784649844.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,6 +1343,116 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-22 15:59</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d43178c04d552e10d659a43cc1e7d446_1784735904.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d2bff71cd90623d9dc0be06bcc9154aa_1784736077.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,6 +1453,116 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5004f3c6f8529fed048e41709832fe2d_1784823030.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cdc7293ed655b883abdbe538ca8364fb_1784823231.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,6 +1563,116 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:54</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d74ca3fbbe04bfe6e3a1eade5bdb0720_1784908397.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:56</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f88b406653fbc697726d92d2d0844a63_1784908558.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,6 +1673,116 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-25 15:37</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/6fd67243106b5b7fb1dede504a670f67.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-25 15:41</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/93a206a45926ed5ec0974b28e113022d.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep11/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,6 +1783,116 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-26 15:38</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/3bc1da00aae3f983285d634c64027b18.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-26 15:41</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/04bd0debd9c376b0606f83c24819a6a7_1785080474.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep12/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/the-vast/series_log.xlsx
+++ b/aimagine/the-vast/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,6 +1893,116 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:41</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/de11af4f856c501098bcc661bf86c9ed.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:45</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/9608b26d86657d41741793e75ff954ae.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-vast/episodes/ep13/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
